--- a/data/trans_orig/Q5417-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Provincia-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68247</t>
+          <t>68791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61746</t>
+          <t>61604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85405</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95128</t>
+          <t>95020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>149525</t>
+          <t>150591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161640</t>
+          <t>161423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73703</t>
+          <t>73601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82385</t>
+          <t>82391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124448</t>
+          <t>124005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133331</t>
+          <t>133320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>50015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121836</t>
+          <t>121543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128614</t>
+          <t>128612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>56860</t>
+          <t>56097</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>66830</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41237</t>
+          <t>40696</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>59265</t>
+          <t>59871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>68961</t>
+          <t>69159</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>103086</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>114651</t>
+          <t>114647</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>101581</t>
+          <t>100968</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>107441</t>
+          <t>107421</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>115981</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>211958</t>
+          <t>212234</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>221227</t>
+          <t>221237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>104486</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>110896</t>
+          <t>110890</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>137481</t>
+          <t>137278</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>149812</t>
+          <t>149667</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>245435</t>
+          <t>245322</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>259508</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>483452</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>495536</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>629853</t>
+          <t>630344</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>653390</t>
+          <t>652980</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1118150</t>
+          <t>1118670</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1144688</t>
+          <t>1145320</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>39365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36756</t>
+          <t>36896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46716</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79960</t>
+          <t>81107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90186</t>
+          <t>90946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72308</t>
+          <t>71455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>83728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97692</t>
+          <t>97753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160918</t>
+          <t>162406</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>175912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -7228,12 +7228,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7313,12 +7313,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>53807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63341</t>
+          <t>62808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75516</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112157</t>
+          <t>111879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126972</t>
+          <t>127025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8023,12 +8023,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55371</t>
+          <t>55495</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63054</t>
+          <t>63079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76590</t>
+          <t>76480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85574</t>
+          <t>84556</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136692</t>
+          <t>135423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147277</t>
+          <t>146595</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8221,12 +8221,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>67556</t>
+          <t>67107</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>78404</t>
+          <t>78418</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53679</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>65422</t>
+          <t>65002</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>102637</t>
+          <t>102659</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>115598</t>
+          <t>115568</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -9730,12 +9730,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9843,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>96587</t>
+          <t>96986</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>110267</t>
+          <t>109983</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>124581</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>136937</t>
+          <t>136956</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>227567</t>
+          <t>227604</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>244968</t>
+          <t>245153</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>109560</t>
+          <t>110291</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>119614</t>
+          <t>119651</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>140878</t>
+          <t>141928</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>157543</t>
+          <t>157584</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>256215</t>
+          <t>256744</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>274620</t>
+          <t>274157</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -10755,12 +10755,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10805,12 +10805,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10868,12 +10868,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>66716</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>522689</t>
+          <t>520565</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>542791</t>
+          <t>541850</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>659558</t>
+          <t>661364</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>692067</t>
+          <t>692557</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1189090</t>
+          <t>1192444</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1227308</t>
+          <t>1228512</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41083</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48360</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77786</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86385</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82455</t>
+          <t>81873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95761</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110175</t>
+          <t>110245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181682</t>
+          <t>181832</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197215</t>
+          <t>196934</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62773</t>
+          <t>62775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12939,12 +12939,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12974,12 +12974,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128685</t>
+          <t>128668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140636</t>
+          <t>140543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>59210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87024</t>
+          <t>86757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149078</t>
+          <t>149139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155469</t>
+          <t>155458</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -14062,7 +14062,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>49408</t>
+          <t>49418</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82594</t>
+          <t>82731</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91500</t>
+          <t>91458</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14147,12 +14147,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14588,12 +14588,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14603,12 +14603,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -14631,12 +14631,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53806</t>
+          <t>53566</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64774</t>
+          <t>64839</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14701,12 +14701,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>98381</t>
+          <t>97867</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>111126</t>
+          <t>111013</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14716,12 +14716,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -14974,12 +14974,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>872</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15044,12 +15044,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -15200,12 +15200,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>99533</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>109491</t>
+          <t>109507</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>128287</t>
+          <t>127996</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>142270</t>
+          <t>142425</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>231834</t>
+          <t>232438</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>249609</t>
+          <t>249179</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15691,12 +15691,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15741,12 +15741,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -15769,12 +15769,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>124453</t>
+          <t>124328</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>133346</t>
+          <t>133355</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>164536</t>
+          <t>164812</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>175014</t>
+          <t>175001</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -15839,12 +15839,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>293461</t>
+          <t>293716</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>306734</t>
+          <t>306812</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16019,34 +16019,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>18432</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>19016</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16162,12 +16162,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -16225,12 +16225,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16240,12 +16240,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>45813</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>58794</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16310,12 +16310,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -16338,12 +16338,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>562283</t>
+          <t>561678</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>578740</t>
+          <t>578810</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16373,12 +16373,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>714900</t>
+          <t>713987</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>744826</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16388,12 +16388,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16408,12 +16408,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1285246</t>
+          <t>1285667</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1318478</t>
+          <t>1318480</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16423,7 +16423,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -16947,32 +16947,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -16982,32 +16982,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -17060,32 +17060,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17095,32 +17095,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -17173,32 +17173,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58919</t>
+          <t>60923</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54194</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>63345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -17208,32 +17208,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>114820</t>
+          <t>121878</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>117326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>124340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -17251,17 +17251,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -17286,17 +17286,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -17321,17 +17321,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -17403,32 +17403,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -17438,32 +17438,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>917</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -17491,12 +17491,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -17526,12 +17526,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17551,32 +17551,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -17594,32 +17594,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -17629,32 +17629,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -17664,32 +17664,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -17707,32 +17707,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74563</t>
+          <t>81759</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>76029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78112</t>
+          <t>85522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -17742,32 +17742,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>115006</t>
+          <t>120444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108241</t>
+          <t>113574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>125987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -17777,32 +17777,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>189568</t>
+          <t>202204</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>180792</t>
+          <t>193242</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>195957</t>
+          <t>208824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -17820,17 +17820,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -17890,17 +17890,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -17947,12 +17947,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -17972,32 +17972,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -18007,22 +18007,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -18060,12 +18060,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>398</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -18095,12 +18095,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -18120,32 +18120,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>398</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -18163,32 +18163,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -18198,32 +18198,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -18233,32 +18233,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -18276,32 +18276,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68107</t>
+          <t>66984</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63534</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70723</t>
+          <t>69814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -18311,32 +18311,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78578</t>
+          <t>77059</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73685</t>
+          <t>72715</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82269</t>
+          <t>80350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18346,32 +18346,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>146685</t>
+          <t>144042</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140543</t>
+          <t>138091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151016</t>
+          <t>148540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -18389,17 +18389,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -18424,17 +18424,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18459,17 +18459,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>911</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -18551,12 +18551,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>911</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -18586,12 +18586,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>867</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>867</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -18699,12 +18699,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -18767,32 +18767,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -18802,32 +18802,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -18880,32 +18880,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>105881</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96276</t>
+          <t>102334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101283</t>
+          <t>108038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -18915,32 +18915,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>173858</t>
+          <t>189037</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170727</t>
+          <t>185839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176183</t>
+          <t>191152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -18958,17 +18958,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -18993,17 +18993,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -19028,17 +19028,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>466</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -19233,12 +19233,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>466</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -19268,12 +19268,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -19301,32 +19301,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -19336,32 +19336,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -19371,17 +19371,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19391,12 +19391,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -19414,32 +19414,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -19449,32 +19449,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54490</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>53243</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56685</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -19484,32 +19484,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>87280</t>
+          <t>91018</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>83426</t>
+          <t>87226</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>89831</t>
+          <t>93611</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -19527,17 +19527,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -19562,17 +19562,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>61197</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>61197</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>61197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -19597,17 +19597,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>93192</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93192</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93192</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -19644,32 +19644,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19679,32 +19679,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19714,32 +19714,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -19870,32 +19870,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>343</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -19905,32 +19905,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -19940,32 +19940,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -19983,27 +19983,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59173</t>
+          <t>59135</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -20018,32 +20018,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>57331</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>62045</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20053,22 +20053,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>114946</t>
+          <t>116768</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>110857</t>
+          <t>112636</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118323</t>
+          <t>119925</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -20096,17 +20096,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -20131,17 +20131,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -20166,17 +20166,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -20248,32 +20248,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -20283,32 +20283,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -20326,7 +20326,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>955</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -20361,32 +20361,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20396,32 +20396,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>875</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -20449,12 +20449,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20474,32 +20474,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20509,32 +20509,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -20552,27 +20552,27 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>121871</t>
+          <t>149511</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>118474</t>
+          <t>145029</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -20587,32 +20587,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>331691</t>
+          <t>154829</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>316535</t>
+          <t>149321</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>337825</t>
+          <t>158843</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20622,32 +20622,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>453562</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>443721</t>
+          <t>298224</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>459942</t>
+          <t>309377</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -20665,17 +20665,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -20700,17 +20700,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20735,17 +20735,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -20905,12 +20905,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -20975,12 +20975,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -21018,12 +21018,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -21043,32 +21043,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -21078,32 +21078,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -21121,27 +21121,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>146321</t>
+          <t>162215</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>143415</t>
+          <t>158678</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -21156,32 +21156,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>181535</t>
+          <t>206507</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>176359</t>
+          <t>199864</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>184315</t>
+          <t>209824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -21191,32 +21191,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>327855</t>
+          <t>368723</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>322164</t>
+          <t>361385</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>372614</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -21234,17 +21234,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -21269,17 +21269,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -21304,17 +21304,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -21361,22 +21361,22 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21386,32 +21386,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21421,32 +21421,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -21464,32 +21464,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21499,32 +21499,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21534,32 +21534,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -21577,32 +21577,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21612,32 +21612,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>41408</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21647,32 +21647,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>64629</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -21690,22 +21690,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>631836</t>
+          <t>696602</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>624285</t>
+          <t>687906</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>637493</t>
+          <t>702606</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21725,32 +21725,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>976739</t>
+          <t>841408</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>958218</t>
+          <t>831017</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1004838</t>
+          <t>852541</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21760,32 +21760,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1608575</t>
+          <t>1538009</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1593038</t>
+          <t>1522743</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1635876</t>
+          <t>1549634</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -21803,17 +21803,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -21838,17 +21838,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -21873,17 +21873,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
